--- a/grammar_input.xlsx
+++ b/grammar_input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polimi365-my.sharepoint.com/personal/10393954_polimi_it/Documents/Privata/Russo/russo-pwa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="212" documentId="11_AD4D5CB4E552A5DACE1C64BDF8DC74745BDEDD8E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B429F58A-4574-4E39-88F0-7615C78AC195}"/>
+  <xr:revisionPtr revIDLastSave="537" documentId="11_AD4D5CB4E552A5DACE1C64BDF8DC74745BDEDD8E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F396B071-78C6-4F2C-877B-24A075632D63}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sostantivi" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="361">
   <si>
     <t>id</t>
   </si>
@@ -472,6 +472,654 @@
   </si>
   <si>
     <t>v0002</t>
+  </si>
+  <si>
+    <t>два</t>
+  </si>
+  <si>
+    <t>due</t>
+  </si>
+  <si>
+    <t>numeri</t>
+  </si>
+  <si>
+    <t>двух</t>
+  </si>
+  <si>
+    <t>двум</t>
+  </si>
+  <si>
+    <t>двумя</t>
+  </si>
+  <si>
+    <t>три</t>
+  </si>
+  <si>
+    <t>трёх</t>
+  </si>
+  <si>
+    <t>трём</t>
+  </si>
+  <si>
+    <t>тремя</t>
+  </si>
+  <si>
+    <t>четыре</t>
+  </si>
+  <si>
+    <t>четырёх</t>
+  </si>
+  <si>
+    <t>четырём</t>
+  </si>
+  <si>
+    <t>четырьмя</t>
+  </si>
+  <si>
+    <t>пять</t>
+  </si>
+  <si>
+    <t>пяти</t>
+  </si>
+  <si>
+    <t>пятью</t>
+  </si>
+  <si>
+    <t>восемь</t>
+  </si>
+  <si>
+    <t>восьми</t>
+  </si>
+  <si>
+    <t>восьмью</t>
+  </si>
+  <si>
+    <t>одиннадцать</t>
+  </si>
+  <si>
+    <t>одиннадцати</t>
+  </si>
+  <si>
+    <t>одиннадцатью</t>
+  </si>
+  <si>
+    <t>пятьдесят</t>
+  </si>
+  <si>
+    <t>пятидесяти</t>
+  </si>
+  <si>
+    <t>ятьюдесятью</t>
+  </si>
+  <si>
+    <t>tre</t>
+  </si>
+  <si>
+    <t>quattro</t>
+  </si>
+  <si>
+    <t>cinque</t>
+  </si>
+  <si>
+    <t>sei</t>
+  </si>
+  <si>
+    <t>undici</t>
+  </si>
+  <si>
+    <t>cinquanta</t>
+  </si>
+  <si>
+    <t>сорок</t>
+  </si>
+  <si>
+    <t>сорока</t>
+  </si>
+  <si>
+    <t>девяносто</t>
+  </si>
+  <si>
+    <t>девяноста</t>
+  </si>
+  <si>
+    <t>сто</t>
+  </si>
+  <si>
+    <t>ста</t>
+  </si>
+  <si>
+    <t>quaranta</t>
+  </si>
+  <si>
+    <t>novanta</t>
+  </si>
+  <si>
+    <t>cento</t>
+  </si>
+  <si>
+    <t>n0008</t>
+  </si>
+  <si>
+    <t>n0009</t>
+  </si>
+  <si>
+    <t>n0010</t>
+  </si>
+  <si>
+    <t>n0011</t>
+  </si>
+  <si>
+    <t>n0012</t>
+  </si>
+  <si>
+    <t>n0013</t>
+  </si>
+  <si>
+    <t>n0014</t>
+  </si>
+  <si>
+    <t>n0015</t>
+  </si>
+  <si>
+    <t>n0016</t>
+  </si>
+  <si>
+    <t>n0017</t>
+  </si>
+  <si>
+    <t>Нести</t>
+  </si>
+  <si>
+    <t>Носить</t>
+  </si>
+  <si>
+    <t>unidirezionale</t>
+  </si>
+  <si>
+    <t>pluridirezionale</t>
+  </si>
+  <si>
+    <t>несу</t>
+  </si>
+  <si>
+    <t>несёшь</t>
+  </si>
+  <si>
+    <t>несёт</t>
+  </si>
+  <si>
+    <t>несём</t>
+  </si>
+  <si>
+    <t>несёте</t>
+  </si>
+  <si>
+    <t>несут</t>
+  </si>
+  <si>
+    <t>носят</t>
+  </si>
+  <si>
+    <t>носите</t>
+  </si>
+  <si>
+    <t>носим</t>
+  </si>
+  <si>
+    <t>носит</t>
+  </si>
+  <si>
+    <t>носишь</t>
+  </si>
+  <si>
+    <t>ношу</t>
+  </si>
+  <si>
+    <t>нёс</t>
+  </si>
+  <si>
+    <t>несла</t>
+  </si>
+  <si>
+    <t>несли</t>
+  </si>
+  <si>
+    <t>неси</t>
+  </si>
+  <si>
+    <t>несите</t>
+  </si>
+  <si>
+    <t>носил</t>
+  </si>
+  <si>
+    <t>носила</t>
+  </si>
+  <si>
+    <t>носили</t>
+  </si>
+  <si>
+    <t>portare a piedi</t>
+  </si>
+  <si>
+    <t>portare a mano</t>
+  </si>
+  <si>
+    <t>Вести</t>
+  </si>
+  <si>
+    <t>Водить</t>
+  </si>
+  <si>
+    <t>веду</t>
+  </si>
+  <si>
+    <t>ведёшь</t>
+  </si>
+  <si>
+    <t>ведёт</t>
+  </si>
+  <si>
+    <t>ведём</t>
+  </si>
+  <si>
+    <t>ведёте</t>
+  </si>
+  <si>
+    <t>ведут</t>
+  </si>
+  <si>
+    <t>вожу</t>
+  </si>
+  <si>
+    <t>водишь</t>
+  </si>
+  <si>
+    <t>водит</t>
+  </si>
+  <si>
+    <t>водим</t>
+  </si>
+  <si>
+    <t>водите</t>
+  </si>
+  <si>
+    <t>водят</t>
+  </si>
+  <si>
+    <t>веди</t>
+  </si>
+  <si>
+    <t>води</t>
+  </si>
+  <si>
+    <t>вёл</t>
+  </si>
+  <si>
+    <t>вела</t>
+  </si>
+  <si>
+    <t>вели</t>
+  </si>
+  <si>
+    <t>водил</t>
+  </si>
+  <si>
+    <t>водила</t>
+  </si>
+  <si>
+    <t>водили</t>
+  </si>
+  <si>
+    <t>portare con un mezzo</t>
+  </si>
+  <si>
+    <t>Везти</t>
+  </si>
+  <si>
+    <t>Возить</t>
+  </si>
+  <si>
+    <t>везу</t>
+  </si>
+  <si>
+    <t>везёшь</t>
+  </si>
+  <si>
+    <t>везёт</t>
+  </si>
+  <si>
+    <t>везём</t>
+  </si>
+  <si>
+    <t>везёте</t>
+  </si>
+  <si>
+    <t>везут</t>
+  </si>
+  <si>
+    <t>возишь</t>
+  </si>
+  <si>
+    <t>возит</t>
+  </si>
+  <si>
+    <t>возим</t>
+  </si>
+  <si>
+    <t>возите</t>
+  </si>
+  <si>
+    <t>возят</t>
+  </si>
+  <si>
+    <t>вёз</t>
+  </si>
+  <si>
+    <t>везла</t>
+  </si>
+  <si>
+    <t>везли</t>
+  </si>
+  <si>
+    <t>вези</t>
+  </si>
+  <si>
+    <t>вози</t>
+  </si>
+  <si>
+    <t>возил</t>
+  </si>
+  <si>
+    <t>возила</t>
+  </si>
+  <si>
+    <t>возили</t>
+  </si>
+  <si>
+    <t>Подниматься</t>
+  </si>
+  <si>
+    <t>поднимáюсь</t>
+  </si>
+  <si>
+    <t>поднимáешься</t>
+  </si>
+  <si>
+    <t>поднимáются</t>
+  </si>
+  <si>
+    <t>подниму́сь</t>
+  </si>
+  <si>
+    <t>подни́мешься</t>
+  </si>
+  <si>
+    <t>подни́мутся</t>
+  </si>
+  <si>
+    <t>salire</t>
+  </si>
+  <si>
+    <t>perfettivo</t>
+  </si>
+  <si>
+    <t>scendere</t>
+  </si>
+  <si>
+    <t>спуска́юсь</t>
+  </si>
+  <si>
+    <t>спуска́ешься</t>
+  </si>
+  <si>
+    <t>спуска́ются</t>
+  </si>
+  <si>
+    <t>спущу́сь</t>
+  </si>
+  <si>
+    <t>спу́стишься</t>
+  </si>
+  <si>
+    <t>спу́стятся</t>
+  </si>
+  <si>
+    <t>поднимáйся</t>
+  </si>
+  <si>
+    <t>поднимáйтесь</t>
+  </si>
+  <si>
+    <t>подними́сь</t>
+  </si>
+  <si>
+    <t>спуска́йся</t>
+  </si>
+  <si>
+    <t>спусти́сь</t>
+  </si>
+  <si>
+    <t>подними́тесь</t>
+  </si>
+  <si>
+    <t>спуска́йтесь</t>
+  </si>
+  <si>
+    <t>спуститесь</t>
+  </si>
+  <si>
+    <t>Спускаться</t>
+  </si>
+  <si>
+    <t>Спуститься</t>
+  </si>
+  <si>
+    <t>двести</t>
+  </si>
+  <si>
+    <t>триста</t>
+  </si>
+  <si>
+    <t>четыреста</t>
+  </si>
+  <si>
+    <t>двухсот</t>
+  </si>
+  <si>
+    <t>трёхсот</t>
+  </si>
+  <si>
+    <t>трёмстам</t>
+  </si>
+  <si>
+    <t>тремястами</t>
+  </si>
+  <si>
+    <t>двумста</t>
+  </si>
+  <si>
+    <t>двумястам</t>
+  </si>
+  <si>
+    <t>двухста</t>
+  </si>
+  <si>
+    <t xml:space="preserve">трёхстах </t>
+  </si>
+  <si>
+    <t xml:space="preserve">четырёхсот </t>
+  </si>
+  <si>
+    <t>четырёмстам</t>
+  </si>
+  <si>
+    <t>четырьмястами</t>
+  </si>
+  <si>
+    <t xml:space="preserve">четырёхстах </t>
+  </si>
+  <si>
+    <t>пятьсот</t>
+  </si>
+  <si>
+    <t>шестьсот</t>
+  </si>
+  <si>
+    <t>пятисот</t>
+  </si>
+  <si>
+    <t>шестисот</t>
+  </si>
+  <si>
+    <t>пятистам</t>
+  </si>
+  <si>
+    <t>шестистам</t>
+  </si>
+  <si>
+    <t>пятьюстами</t>
+  </si>
+  <si>
+    <t>шестьюстами</t>
+  </si>
+  <si>
+    <t>пятистах</t>
+  </si>
+  <si>
+    <t>шестистах</t>
+  </si>
+  <si>
+    <t xml:space="preserve">тысяча </t>
+  </si>
+  <si>
+    <t>тысячу</t>
+  </si>
+  <si>
+    <t>тысячи</t>
+  </si>
+  <si>
+    <t>миллион</t>
+  </si>
+  <si>
+    <t>миллионы</t>
+  </si>
+  <si>
+    <t>тысяч</t>
+  </si>
+  <si>
+    <t>миллиона</t>
+  </si>
+  <si>
+    <t>миллионов</t>
+  </si>
+  <si>
+    <t>тысячe</t>
+  </si>
+  <si>
+    <t>тысячам</t>
+  </si>
+  <si>
+    <t>миллиону</t>
+  </si>
+  <si>
+    <t>миллионам</t>
+  </si>
+  <si>
+    <t>тысячей</t>
+  </si>
+  <si>
+    <t>тысячами</t>
+  </si>
+  <si>
+    <t>миллионом</t>
+  </si>
+  <si>
+    <t>миллионами</t>
+  </si>
+  <si>
+    <t>тысяче</t>
+  </si>
+  <si>
+    <t>тысячах</t>
+  </si>
+  <si>
+    <t>миллионе</t>
+  </si>
+  <si>
+    <t>миллионах</t>
+  </si>
+  <si>
+    <t>duecento</t>
+  </si>
+  <si>
+    <t>trecento</t>
+  </si>
+  <si>
+    <t>quattrocento</t>
+  </si>
+  <si>
+    <t>cinquecento</t>
+  </si>
+  <si>
+    <t>seicento</t>
+  </si>
+  <si>
+    <t>mille</t>
+  </si>
+  <si>
+    <t>milione</t>
+  </si>
+  <si>
+    <t>n0018</t>
+  </si>
+  <si>
+    <t>n0019</t>
+  </si>
+  <si>
+    <t>n0020</t>
+  </si>
+  <si>
+    <t>n0021</t>
+  </si>
+  <si>
+    <t>n0022</t>
+  </si>
+  <si>
+    <t>n0023</t>
+  </si>
+  <si>
+    <t>n0024</t>
+  </si>
+  <si>
+    <t>v0003</t>
+  </si>
+  <si>
+    <t>v0004</t>
+  </si>
+  <si>
+    <t>v0005</t>
+  </si>
+  <si>
+    <t>v0006</t>
+  </si>
+  <si>
+    <t>v0007</t>
+  </si>
+  <si>
+    <t>v0008</t>
+  </si>
+  <si>
+    <t>v0009</t>
+  </si>
+  <si>
+    <t>v0010</t>
+  </si>
+  <si>
+    <t>v0011</t>
+  </si>
+  <si>
+    <t>v0012</t>
   </si>
 </sst>
 </file>
@@ -795,7 +1443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -1231,16 +1879,639 @@
         <v>95</v>
       </c>
     </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E9" t="s">
+        <v>147</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="N9" t="s">
+        <v>145</v>
+      </c>
+      <c r="O9" t="s">
+        <v>148</v>
+      </c>
+      <c r="P9" t="s">
+        <v>149</v>
+      </c>
+      <c r="R9" t="s">
+        <v>150</v>
+      </c>
+      <c r="S9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" t="s">
+        <v>171</v>
+      </c>
+      <c r="E10" t="s">
+        <v>147</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="N10" t="s">
+        <v>151</v>
+      </c>
+      <c r="O10" t="s">
+        <v>152</v>
+      </c>
+      <c r="P10" t="s">
+        <v>153</v>
+      </c>
+      <c r="R10" t="s">
+        <v>154</v>
+      </c>
+      <c r="S10" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>188</v>
+      </c>
+      <c r="B11" t="s">
+        <v>155</v>
+      </c>
+      <c r="C11" t="s">
+        <v>172</v>
+      </c>
+      <c r="E11" t="s">
+        <v>147</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="N11" t="s">
+        <v>155</v>
+      </c>
+      <c r="O11" t="s">
+        <v>156</v>
+      </c>
+      <c r="P11" t="s">
+        <v>157</v>
+      </c>
+      <c r="R11" t="s">
+        <v>158</v>
+      </c>
+      <c r="S11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>189</v>
+      </c>
+      <c r="B12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C12" t="s">
+        <v>173</v>
+      </c>
+      <c r="E12" t="s">
+        <v>147</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
+        <v>159</v>
+      </c>
+      <c r="I12" t="s">
+        <v>160</v>
+      </c>
+      <c r="J12" t="s">
+        <v>160</v>
+      </c>
+      <c r="K12" t="s">
+        <v>159</v>
+      </c>
+      <c r="L12" t="s">
+        <v>161</v>
+      </c>
+      <c r="M12" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>190</v>
+      </c>
+      <c r="B13" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" t="s">
+        <v>174</v>
+      </c>
+      <c r="E13" t="s">
+        <v>147</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>162</v>
+      </c>
+      <c r="I13" t="s">
+        <v>163</v>
+      </c>
+      <c r="J13" t="s">
+        <v>163</v>
+      </c>
+      <c r="K13" t="s">
+        <v>162</v>
+      </c>
+      <c r="L13" t="s">
+        <v>164</v>
+      </c>
+      <c r="M13" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B14" t="s">
+        <v>165</v>
+      </c>
+      <c r="C14" t="s">
+        <v>175</v>
+      </c>
+      <c r="E14" t="s">
+        <v>147</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>165</v>
+      </c>
+      <c r="I14" t="s">
+        <v>166</v>
+      </c>
+      <c r="J14" t="s">
+        <v>166</v>
+      </c>
+      <c r="K14" t="s">
+        <v>165</v>
+      </c>
+      <c r="L14" t="s">
+        <v>167</v>
+      </c>
+      <c r="M14" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>192</v>
+      </c>
+      <c r="B15" t="s">
+        <v>168</v>
+      </c>
+      <c r="C15" t="s">
+        <v>176</v>
+      </c>
+      <c r="E15" t="s">
+        <v>147</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>168</v>
+      </c>
+      <c r="I15" t="s">
+        <v>169</v>
+      </c>
+      <c r="J15" t="s">
+        <v>169</v>
+      </c>
+      <c r="K15" t="s">
+        <v>168</v>
+      </c>
+      <c r="L15" t="s">
+        <v>170</v>
+      </c>
+      <c r="M15" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>193</v>
+      </c>
+      <c r="B16" t="s">
+        <v>177</v>
+      </c>
+      <c r="C16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E16" t="s">
+        <v>147</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
+        <v>177</v>
+      </c>
+      <c r="I16" t="s">
+        <v>178</v>
+      </c>
+      <c r="J16" t="s">
+        <v>178</v>
+      </c>
+      <c r="K16" t="s">
+        <v>177</v>
+      </c>
+      <c r="L16" t="s">
+        <v>178</v>
+      </c>
+      <c r="M16" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>194</v>
+      </c>
+      <c r="B17" t="s">
+        <v>179</v>
+      </c>
+      <c r="C17" t="s">
+        <v>184</v>
+      </c>
+      <c r="E17" t="s">
+        <v>147</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
+        <v>179</v>
+      </c>
+      <c r="I17" t="s">
+        <v>180</v>
+      </c>
+      <c r="J17" t="s">
+        <v>180</v>
+      </c>
+      <c r="K17" t="s">
+        <v>179</v>
+      </c>
+      <c r="L17" t="s">
+        <v>180</v>
+      </c>
+      <c r="M17" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C18" t="s">
+        <v>185</v>
+      </c>
+      <c r="E18" t="s">
+        <v>147</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
+        <v>181</v>
+      </c>
+      <c r="I18" t="s">
+        <v>182</v>
+      </c>
+      <c r="J18" t="s">
+        <v>182</v>
+      </c>
+      <c r="K18" t="s">
+        <v>181</v>
+      </c>
+      <c r="L18" t="s">
+        <v>182</v>
+      </c>
+      <c r="M18" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>344</v>
+      </c>
+      <c r="B19" t="s">
+        <v>292</v>
+      </c>
+      <c r="C19" t="s">
+        <v>337</v>
+      </c>
+      <c r="E19" t="s">
+        <v>147</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="N19" t="s">
+        <v>292</v>
+      </c>
+      <c r="O19" t="s">
+        <v>295</v>
+      </c>
+      <c r="P19" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>292</v>
+      </c>
+      <c r="R19" t="s">
+        <v>300</v>
+      </c>
+      <c r="S19" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>345</v>
+      </c>
+      <c r="B20" t="s">
+        <v>293</v>
+      </c>
+      <c r="C20" t="s">
+        <v>338</v>
+      </c>
+      <c r="E20" t="s">
+        <v>147</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="N20" t="s">
+        <v>293</v>
+      </c>
+      <c r="O20" t="s">
+        <v>296</v>
+      </c>
+      <c r="P20" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>293</v>
+      </c>
+      <c r="R20" t="s">
+        <v>298</v>
+      </c>
+      <c r="S20" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>346</v>
+      </c>
+      <c r="B21" t="s">
+        <v>294</v>
+      </c>
+      <c r="C21" t="s">
+        <v>339</v>
+      </c>
+      <c r="E21" t="s">
+        <v>147</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="N21" t="s">
+        <v>294</v>
+      </c>
+      <c r="O21" t="s">
+        <v>303</v>
+      </c>
+      <c r="P21" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>294</v>
+      </c>
+      <c r="R21" t="s">
+        <v>305</v>
+      </c>
+      <c r="S21" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>347</v>
+      </c>
+      <c r="B22" t="s">
+        <v>307</v>
+      </c>
+      <c r="C22" t="s">
+        <v>340</v>
+      </c>
+      <c r="E22" t="s">
+        <v>147</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="N22" t="s">
+        <v>307</v>
+      </c>
+      <c r="O22" t="s">
+        <v>309</v>
+      </c>
+      <c r="P22" t="s">
+        <v>311</v>
+      </c>
+      <c r="R22" t="s">
+        <v>313</v>
+      </c>
+      <c r="S22" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>348</v>
+      </c>
+      <c r="B23" t="s">
+        <v>308</v>
+      </c>
+      <c r="C23" t="s">
+        <v>341</v>
+      </c>
+      <c r="E23" t="s">
+        <v>147</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="N23" t="s">
+        <v>308</v>
+      </c>
+      <c r="O23" t="s">
+        <v>310</v>
+      </c>
+      <c r="P23" t="s">
+        <v>312</v>
+      </c>
+      <c r="R23" t="s">
+        <v>314</v>
+      </c>
+      <c r="S23" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>349</v>
+      </c>
+      <c r="B24" t="s">
+        <v>317</v>
+      </c>
+      <c r="C24" t="s">
+        <v>342</v>
+      </c>
+      <c r="E24" t="s">
+        <v>147</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="s">
+        <v>317</v>
+      </c>
+      <c r="I24" t="s">
+        <v>319</v>
+      </c>
+      <c r="J24" t="s">
+        <v>325</v>
+      </c>
+      <c r="K24" t="s">
+        <v>318</v>
+      </c>
+      <c r="L24" t="s">
+        <v>329</v>
+      </c>
+      <c r="M24" t="s">
+        <v>333</v>
+      </c>
+      <c r="N24" t="s">
+        <v>319</v>
+      </c>
+      <c r="O24" t="s">
+        <v>322</v>
+      </c>
+      <c r="P24" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>319</v>
+      </c>
+      <c r="R24" t="s">
+        <v>330</v>
+      </c>
+      <c r="S24" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>350</v>
+      </c>
+      <c r="B25" t="s">
+        <v>320</v>
+      </c>
+      <c r="C25" t="s">
+        <v>343</v>
+      </c>
+      <c r="E25" t="s">
+        <v>147</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="H25" t="s">
+        <v>320</v>
+      </c>
+      <c r="I25" t="s">
+        <v>323</v>
+      </c>
+      <c r="J25" t="s">
+        <v>327</v>
+      </c>
+      <c r="K25" t="s">
+        <v>320</v>
+      </c>
+      <c r="L25" t="s">
+        <v>331</v>
+      </c>
+      <c r="M25" t="s">
+        <v>335</v>
+      </c>
+      <c r="N25" t="s">
+        <v>321</v>
+      </c>
+      <c r="O25" t="s">
+        <v>324</v>
+      </c>
+      <c r="P25" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>321</v>
+      </c>
+      <c r="R25" t="s">
+        <v>332</v>
+      </c>
+      <c r="S25" t="s">
+        <v>336</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93E99B39-AECC-450A-B454-5F32EF9A7748}">
-  <dimension ref="A1:Y3"/>
+  <dimension ref="A1:Y13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1330,7 +2601,7 @@
         <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>198</v>
       </c>
       <c r="E2" t="s">
         <v>117</v>
@@ -1386,7 +2657,7 @@
         <v>131</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>198</v>
       </c>
       <c r="E3" t="s">
         <v>117</v>
@@ -1423,6 +2694,452 @@
       </c>
       <c r="W3" t="s">
         <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" t="s">
+        <v>221</v>
+      </c>
+      <c r="D4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>200</v>
+      </c>
+      <c r="I4" t="s">
+        <v>201</v>
+      </c>
+      <c r="J4" t="s">
+        <v>202</v>
+      </c>
+      <c r="K4" t="s">
+        <v>203</v>
+      </c>
+      <c r="L4" t="s">
+        <v>204</v>
+      </c>
+      <c r="M4" t="s">
+        <v>205</v>
+      </c>
+      <c r="T4" t="s">
+        <v>212</v>
+      </c>
+      <c r="U4" t="s">
+        <v>213</v>
+      </c>
+      <c r="W4" t="s">
+        <v>214</v>
+      </c>
+      <c r="X4" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>352</v>
+      </c>
+      <c r="B5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C5" t="s">
+        <v>221</v>
+      </c>
+      <c r="D5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>211</v>
+      </c>
+      <c r="I5" t="s">
+        <v>210</v>
+      </c>
+      <c r="J5" t="s">
+        <v>209</v>
+      </c>
+      <c r="K5" t="s">
+        <v>208</v>
+      </c>
+      <c r="L5" t="s">
+        <v>207</v>
+      </c>
+      <c r="M5" t="s">
+        <v>206</v>
+      </c>
+      <c r="T5" t="s">
+        <v>217</v>
+      </c>
+      <c r="U5" t="s">
+        <v>218</v>
+      </c>
+      <c r="W5" t="s">
+        <v>219</v>
+      </c>
+      <c r="X5" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>353</v>
+      </c>
+      <c r="B6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C6" t="s">
+        <v>220</v>
+      </c>
+      <c r="D6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E6" t="s">
+        <v>117</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>224</v>
+      </c>
+      <c r="I6" t="s">
+        <v>225</v>
+      </c>
+      <c r="J6" t="s">
+        <v>226</v>
+      </c>
+      <c r="K6" t="s">
+        <v>227</v>
+      </c>
+      <c r="L6" t="s">
+        <v>228</v>
+      </c>
+      <c r="M6" t="s">
+        <v>229</v>
+      </c>
+      <c r="T6" t="s">
+        <v>238</v>
+      </c>
+      <c r="U6" t="s">
+        <v>239</v>
+      </c>
+      <c r="W6" t="s">
+        <v>240</v>
+      </c>
+      <c r="X6" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>354</v>
+      </c>
+      <c r="B7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C7" t="s">
+        <v>220</v>
+      </c>
+      <c r="D7" t="s">
+        <v>199</v>
+      </c>
+      <c r="E7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>230</v>
+      </c>
+      <c r="I7" t="s">
+        <v>231</v>
+      </c>
+      <c r="J7" t="s">
+        <v>232</v>
+      </c>
+      <c r="K7" t="s">
+        <v>233</v>
+      </c>
+      <c r="L7" t="s">
+        <v>234</v>
+      </c>
+      <c r="M7" t="s">
+        <v>235</v>
+      </c>
+      <c r="T7" t="s">
+        <v>241</v>
+      </c>
+      <c r="U7" t="s">
+        <v>242</v>
+      </c>
+      <c r="W7" t="s">
+        <v>243</v>
+      </c>
+      <c r="X7" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>355</v>
+      </c>
+      <c r="B8" t="s">
+        <v>245</v>
+      </c>
+      <c r="C8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E8" t="s">
+        <v>117</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>247</v>
+      </c>
+      <c r="I8" t="s">
+        <v>248</v>
+      </c>
+      <c r="J8" t="s">
+        <v>249</v>
+      </c>
+      <c r="K8" t="s">
+        <v>250</v>
+      </c>
+      <c r="L8" t="s">
+        <v>251</v>
+      </c>
+      <c r="M8" t="s">
+        <v>252</v>
+      </c>
+      <c r="T8" t="s">
+        <v>258</v>
+      </c>
+      <c r="U8" t="s">
+        <v>259</v>
+      </c>
+      <c r="W8" t="s">
+        <v>260</v>
+      </c>
+      <c r="X8" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>356</v>
+      </c>
+      <c r="B9" t="s">
+        <v>246</v>
+      </c>
+      <c r="C9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D9" t="s">
+        <v>199</v>
+      </c>
+      <c r="E9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>230</v>
+      </c>
+      <c r="I9" t="s">
+        <v>253</v>
+      </c>
+      <c r="J9" t="s">
+        <v>254</v>
+      </c>
+      <c r="K9" t="s">
+        <v>255</v>
+      </c>
+      <c r="L9" t="s">
+        <v>256</v>
+      </c>
+      <c r="M9" t="s">
+        <v>257</v>
+      </c>
+      <c r="T9" t="s">
+        <v>263</v>
+      </c>
+      <c r="U9" t="s">
+        <v>264</v>
+      </c>
+      <c r="W9" t="s">
+        <v>265</v>
+      </c>
+      <c r="X9" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>357</v>
+      </c>
+      <c r="B10" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" t="s">
+        <v>273</v>
+      </c>
+      <c r="D10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>267</v>
+      </c>
+      <c r="I10" t="s">
+        <v>268</v>
+      </c>
+      <c r="M10" t="s">
+        <v>269</v>
+      </c>
+      <c r="X10" t="s">
+        <v>282</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>358</v>
+      </c>
+      <c r="B11" t="s">
+        <v>266</v>
+      </c>
+      <c r="C11" t="s">
+        <v>273</v>
+      </c>
+      <c r="D11" t="s">
+        <v>274</v>
+      </c>
+      <c r="E11" t="s">
+        <v>117</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>270</v>
+      </c>
+      <c r="I11" t="s">
+        <v>271</v>
+      </c>
+      <c r="M11" t="s">
+        <v>272</v>
+      </c>
+      <c r="X11" t="s">
+        <v>284</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>359</v>
+      </c>
+      <c r="B12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C12" t="s">
+        <v>275</v>
+      </c>
+      <c r="D12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" t="s">
+        <v>117</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
+        <v>276</v>
+      </c>
+      <c r="I12" t="s">
+        <v>277</v>
+      </c>
+      <c r="M12" t="s">
+        <v>278</v>
+      </c>
+      <c r="X12" t="s">
+        <v>285</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>360</v>
+      </c>
+      <c r="B13" t="s">
+        <v>291</v>
+      </c>
+      <c r="C13" t="s">
+        <v>275</v>
+      </c>
+      <c r="D13" t="s">
+        <v>274</v>
+      </c>
+      <c r="E13" t="s">
+        <v>117</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>279</v>
+      </c>
+      <c r="I13" t="s">
+        <v>280</v>
+      </c>
+      <c r="M13" t="s">
+        <v>281</v>
+      </c>
+      <c r="X13" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>289</v>
       </c>
     </row>
   </sheetData>
